--- a/sections/03-reproduce-functions/01-calc-amounts/example/data/sales.xlsx
+++ b/sections/03-reproduce-functions/01-calc-amounts/example/data/sales.xlsx
@@ -1229,5 +1229,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdButtons"/>
 </worksheet>
 </file>